--- a/C언어_필기.xlsx
+++ b/C언어_필기.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4002F302-7FEF-452E-9D83-872EBAB3271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4690C12F-5C19-4421-99C0-C0F7A8524AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
   </bookViews>
   <sheets>
     <sheet name="포인터" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,10 @@
     <sheet name="반복문" sheetId="8" r:id="rId7"/>
     <sheet name="비쥬얼 스튜디오" sheetId="7" r:id="rId8"/>
     <sheet name="전처리기" sheetId="4" r:id="rId9"/>
-    <sheet name="디버깅" sheetId="5" r:id="rId10"/>
-    <sheet name="알고리즘" sheetId="6" r:id="rId11"/>
+    <sheet name="컴파일" sheetId="13" r:id="rId10"/>
+    <sheet name="연산자" sheetId="12" r:id="rId11"/>
+    <sheet name="디버깅" sheetId="5" r:id="rId12"/>
+    <sheet name="알고리즘" sheetId="6" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="413">
   <si>
     <t>(1)의미 : 주소값을 저장하는 메모리 공간</t>
   </si>
@@ -224,9 +226,6 @@
     <t>(2) 사용법 예시 : char* name = NULL;</t>
   </si>
   <si>
-    <t>name = (char*)malloc(sizeof(char) * 100); /*명시적 형변환을 한이유는 malloc 함수가 보이드 포인터형으로 리턴하기 때문이다. sizeof를 사용한 이유는 float,long같은자료형은 CPU에 따라서 사이즈가</t>
-  </si>
-  <si>
     <t>다르게 처리되기때문에 그런경우에 대응하기 위해서*/</t>
   </si>
   <si>
@@ -398,673 +397,1062 @@
     <t xml:space="preserve">(1) 입력종료조건에서 우항의 값이 EOF를 사용하면 buffer함수 </t>
   </si>
   <si>
-    <t>ex ) getchar</t>
-  </si>
-  <si>
     <t>(2) 우항의 값이 EOF가 아니라 임의의 문자를 사용하면 buffer를 사용하지 않는 함수</t>
   </si>
   <si>
+    <t>6. gets</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. fgets()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. buffer 함수인지 아닌지 판별하는 법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 운영체제가 하는일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. EOF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 문자인코딩 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)세세하지않고 일반적으로 뭉뚱그려서 비교하면 ASCII코드 방식과 UNI코드 방식으로 나뉜다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)ASCII코드 : ansi에서 만든 문자 하나당 1바이트 공간을 할당 하는 인코딩 방식 8비트중에 7비트만 문자 데이터 저장용으로 사용하고 1비트는 에러체크용 총 128(7비트)개의 문자의 코드값을 부여함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ansi에서 만들었기 때문에 미국 국내용으로 만들어진 코드다. 따라서 영어위주로 만들어져있다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)ansi : 미국 국가표준 협회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4)ansi 코드 : ansi에서 ASCII코드를 확장해서 만든 인코딩방식 에러비트를 없애서 8비트 모두 문자 코드값이 부여됨 총 256(8비트)문자에 대한 코드값이 부여. 미국 국내용으로 만들었음.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MS에서 O/S나 응용프로그램을 만들때 문자인코딩방식으로 ansi 코드를 사용함. Python에서도 기본 인코딩 방식이 ansi코드다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예를 들어서, 메모장(default 인코딩 설정값이 utf-8)에서 쓴 내용을 Python(default 디코딩 설정값이 ansi)에서 불러오려면 저장할때 ansi로 맞춰서 저장하거나, Python 함수의 기본 디코딩 방식을 utf-8로 설정해야 한다. Default 옵션쓰면 디코딩방식이 다르기 때문에 에러남.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5)CP949코드 : MS에서 만든 한국어 지원 ansi 확장코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만약 컴퓨터에 설치되어 있는 윈도우가 영어판 윈도우면 거기서 사용하는 문자 인코딩,디코딩방식은 ansi코드를 쓴다. 만약 윈도우가 한글판이면 ansi코드중에서 CP949를 씀.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예 : 만약 윈도우가 중국어판 윈도우면 문자 인코딩,디코딩 방식으로 ansi확장판으로 cp936등이 사용된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(7)에러처리 방식 : 문자데이터와 별개의 비트를 추가해서 그비트를 이용해서 에러 정보를 교환한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6)utf-8 : 가장 많이 사용하는 UNI코드다. 영어문자(ASCII코드에 있는 문자)는 1바이트(ASCII코드)를 쓰고, 비영어권 문자는 2바이트(UNI 코드)를 쓴다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 컴파일전에 처리 되는 코드</t>
+  </si>
+  <si>
+    <t>(2)위치: 어디든지 상관없다 메인안이여도 처리된다.</t>
+  </si>
+  <si>
+    <t>2. 전처리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 그 함수가 정의되어 있지 않다.</t>
+  </si>
+  <si>
+    <t>(2)해결법 : 오타가 있는지 찾아본다. 또는 #include를 했는지 확인 또는 함수가 퇴출당했는지 찾아본다.</t>
+  </si>
+  <si>
+    <t>1. 에러 싸인 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#include &lt;stdio.h&gt;</t>
+  </si>
+  <si>
+    <t>int CW(char* s); //함수원형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main() </t>
+  </si>
+  <si>
+    <t>int wc = CW("the c book"); //함수호출</t>
+  </si>
+  <si>
+    <t>printf("%d", wc); //값출력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int CW(char* s) </t>
+  </si>
+  <si>
+    <t>int i, wc = 0, waitung = 1; //변수 선언과 초기화</t>
+  </si>
+  <si>
+    <t>for (i = 0;s[i] != NULL; ++i) //조건식 : i를 0으로 초기화, 배열의 i인덱스가 null이 아닐때(문장끝인지 아닌지 판별 '\0'=0=NULL=문자열의 끝 ), i +1추가</t>
+  </si>
+  <si>
+    <t>if (isalpha(s[i])) //포인터 s가 참조하는 데이터 영역의 문자열 리터럴(the c book)의 i번째 요소가 알파벳인지 체크</t>
+  </si>
+  <si>
+    <t>if (waitung) //waitung이 0이 아닌 값일때만 바디실행</t>
+  </si>
+  <si>
+    <t>wc++; //wc값(단어의 개수) 1증가</t>
+  </si>
+  <si>
+    <t>waitung = 0; //waitung값 0으로 초기화</t>
+  </si>
+  <si>
+    <t>else  //포인터 s가 참조하는 데이터 영역의 문자열 리터럴이 알파벳이 아닐때 바디실행</t>
+  </si>
+  <si>
+    <t>waitung = 1; //waitung값 1로 초기화</t>
+  </si>
+  <si>
+    <t>return wc; //for문이 끝나고 최종적으로 체크가 끝난 wc(단어의 개수)를 뱉어냄</t>
+  </si>
+  <si>
+    <t>1. 문자열에서 단어 개수 세는 알고리즘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) typedef 의미 : 새로운 자료형 정의 a와 같은자료형을 b라는 이름으로 '새로운' 자료형을 만들어 낸다(a는 그대로 보존,b가 새로 생성) ex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2-2)typedef 사용이유 : 자료형의 이름으로 그 변수가 무슨 의미인지 파악하기 쉽고, 플랫폼이 다른경우 소스코드를 따로 적어야하지만 typedef를 사용함으로써 플랫폼에 알맞는 자료형이 자동으로 </t>
+  </si>
+  <si>
+    <t>사용되도록 만들 수 있다 (#if 사용)</t>
+  </si>
+  <si>
+    <t>(2-3) typedef 기존자료형이름 새로 만들 자료형이름</t>
+  </si>
+  <si>
+    <t>#ifdef _WIN64 //윈도우 64비트가 깔려있는 컴퓨터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef unsigned __int64 size_t; //64비트용 정수 자료형이 size_t로 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef __int64          ptrdiff_t;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef __int64          intptr_t;</t>
+  </si>
+  <si>
+    <t>#else // O/S가 64비트가 아니라면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef unsigned int     size_t; //일반정수자료형(부호가없는)이 size_t로 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef int              ptrdiff_t;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef int              intptr_t;</t>
+  </si>
+  <si>
+    <t>#endif</t>
+  </si>
+  <si>
+    <t>(3) 차이점 :#define은 a를 b로 대체하는 것이고(자료형 x) typedef는 a는 보존한채 b라는 새로운 자료형 창조</t>
+  </si>
+  <si>
+    <t>3. #define과 typedef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)dst = destination (목적지)</t>
+  </si>
+  <si>
+    <t>(2)src = source (원본)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)cat = concatenate (연결한다) </t>
+  </si>
+  <si>
+    <t>(3-2) 예시 : "hi" + " Tom"</t>
+  </si>
+  <si>
+    <t>-&gt; "hi Tom"</t>
+  </si>
+  <si>
+    <t>(4)cmp = compare (비교하다)</t>
+  </si>
+  <si>
+    <t>(5)chr = character (문자)</t>
+  </si>
+  <si>
+    <t>(6)loc = location (위치)</t>
+  </si>
+  <si>
+    <t>3. 많이 쓰이는 매개변수명 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) Solution Explore -&gt; 프로젝트 이름 -&gt; 우클릭 -&gt; Properties -&gt; General -&gt; SDL checks </t>
+  </si>
+  <si>
+    <t>1. SDL 체크 해제 하는법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PID : prcess ID (운영체제가 프로세스를 식별하기 위해 부여한 식별번호)</t>
+  </si>
+  <si>
+    <t>4. process : 실행중인 프로그램을 프로세스라 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆4?쇌</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>Press any key to close this window . . .</t>
+  </si>
+  <si>
+    <t>unresolved external symbol ~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:\Users\USER\source\repos\Project62\x64\Debug\Project62.exe (process 5432) exited with code 0.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)해결법 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 정상적으로 프로그램이 실행되고 끝났다는 의미 하지만 원하는 방식으로 프로그램이 처리된게 아닐수도 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) A + B로 연결, concatenate기능을 함수로 구현</t>
+  </si>
+  <si>
+    <t>(2)예시 : char dst[12] = "hello";</t>
+  </si>
+  <si>
+    <t>char src[7] = " world";</t>
+  </si>
+  <si>
+    <t>strcat(dst, src);</t>
+  </si>
+  <si>
+    <t>printf("%s", dst);</t>
+  </si>
+  <si>
+    <t>(1) 의미 : 토큰은 문법적으로 더이상 나눌수 없는 기본적인 요소(공백으로 분리된 단어각각을 의미) 예시 "I am a boy" //여기서 토큰은 "I","am","a","boy" 4개로 존재</t>
+  </si>
+  <si>
+    <t>(1)atoi : str을 int형으로 변환한다</t>
+  </si>
+  <si>
+    <t>(2)atof : str을 double형으로 변환한다.</t>
+  </si>
+  <si>
+    <t>(3) 예시</t>
+  </si>
+  <si>
+    <t>5. strcat(A, B)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. token</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. atoi, atof 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)컴파일할때 실행파일의 헤더에 메인함수의 주소 위치정보가 같이 포함된채로 exe가 완성된다.</t>
+  </si>
+  <si>
+    <t>(2)exe를 실행하면 O/S가 메모리에 코드영역에서 메인함수의 위치정보를 알아내서 메인함수 호출</t>
+  </si>
+  <si>
+    <t>(3)STACK영역에 메인함수의 바디 데이터가 저장되고 O/S는 그 데이터를 보고 프로세스 진행</t>
+  </si>
+  <si>
+    <t>5. main()함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미: continue를 만나면 for문에선 증감식, while문에서는 조건식으로 간다.</t>
+  </si>
+  <si>
+    <t>1. continue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. 함수에서 선언된 포인터형 변수(지역변수)를 리턴하면 안된다 왜냐하면 함수종료후에 포인터형 변수가 참조하고 있는 주소위치의 데이터가 운영체제의 의해 삭제되기 때문이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. strlen()함수 유의사항 : 널문자는 개수에 포함을 안시키기 때문에 for문에서 두번째 조건식에 strlen 함수사용시 조심해야 한다. 문자배열에 요소하나씩 대입시킬때 널문자를 반드시 포함시켜줘야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)포인터형으로 리턴한다(배열형으로 리턴하는건 문법에러)</t>
+  </si>
+  <si>
+    <t>(2)함수에서 리턴하지말고 call by reference를 활용하여 원본 또는 caller에서 수정될 배열을 선언하고 그 배열을 함수로 전달받아서 수정한다.</t>
+  </si>
+  <si>
+    <t>12. 함수에서 배열리턴해야할때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)정의 : struct tag이름 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 바디(함수는 바디에 포함 안됨)</t>
+  </si>
+  <si>
+    <t>}; // 정의와 동시에 구조체 변수 선언은 C언어 책521P 참고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)변수선언 : (1)에서 구조체를 정의한후 struct tag x; </t>
+  </si>
+  <si>
+    <t>(3)구조체는 생김새는 클래스와 비슷하지만, 기본자료형이다. 참조변수X</t>
+  </si>
+  <si>
+    <t>(4)구조체 멤버변수로 포인터를 가지고있을때 초기화를 안해두면 default값으로 NULL이 된다.</t>
+  </si>
+  <si>
+    <t>1. 구조체(struct)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex) int* p;</t>
+  </si>
+  <si>
+    <t>int x = 7;</t>
+  </si>
+  <si>
+    <t>p = &amp;x;</t>
+  </si>
+  <si>
+    <t>ex) int x = 7;</t>
+  </si>
+  <si>
+    <t>int y;</t>
+  </si>
+  <si>
+    <t>y = x; //깊은복사의 예</t>
+  </si>
+  <si>
+    <t>13.얕은 복사 : 주소값만 복사 얕은복사는 =으로 구현함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14. 깊은 복사 : 데이터를 복사 깊은복사는 보통 함수를 제공함(ex) strcpy())</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p.구조체멤버변수이름; //에러남</t>
+  </si>
+  <si>
+    <t>15. 간접참조 연산자(*)를 사용하는경우 : (*p).구조체 멤버변수이름; // ()치는 이유 : .연산자가 *보다 연산자 우선순위가 빠르기 때문이다. 따라서 *p.구조체 멤벼변수를 쓰면 p.구조체멤버변수로 처리되고 그이후 *이 따로 처리된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16. 간접멤버연산자(-&gt;)를 사용하는경우 : p-&gt;구조체 멤버변수이름;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)double이 float보다 정확하다.</t>
+  </si>
+  <si>
+    <t>1. float과 double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)메모리 크기 : 공용체는 풀워드단위(하프워드 : 2바이트 풀워드 : 4바이트 더블워드 : 8바이트)로 끊기때문에 4바이트씩 끊어져야한다</t>
+  </si>
+  <si>
+    <t>2. 공용체(union)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 메모리 크기 : 4바이트(내부적으로는 정수형으로 처리된다)</t>
+  </si>
+  <si>
+    <t>(2)사용처 : 예측할 수 없는 값의 입력을 방지하기위해서 enum을 사용한다. 그리고 enum의 요소값으로 의미있는 상수이름을 부여함으로써 상수값지정할때 혼동을 방지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3) 예시 : </t>
+  </si>
+  <si>
+    <t>2. enum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)주의사항 : math.h에 함수원형이 저장되어 있다.</t>
+  </si>
+  <si>
+    <t>1. abs() (절댓값을 리턴해주는 함수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>struct food a[] = {</t>
+  </si>
+  <si>
+    <t>{"bubble gum",1000}</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>printf("%s %d",a[0].name,a[0].c);</t>
+  </si>
+  <si>
+    <t>(1)struct food a[2];</t>
+  </si>
+  <si>
+    <t>a-&gt;c = 1000; //첫번째 요소</t>
+  </si>
+  <si>
+    <t>strcpy(a-&gt;name, "kimch");</t>
+  </si>
+  <si>
+    <t>(a + 1)-&gt;c = 2000; //두번째 요소</t>
+  </si>
+  <si>
+    <t>strcpy((a + 1)-&gt;name, "gum");</t>
+  </si>
+  <si>
+    <t>printf("%s %d",(a+1)-&gt;name,(a+1)-&gt;c);</t>
+  </si>
+  <si>
+    <t>3. 배열 .연사자를 이용한 표기법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 구조체 배열에서 요소값을 포인터방식으로 설정하는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 리터럴 : 값(데이터)가 저장되는 공간 항상 데이터 영역에 존재함 다른값을 대입받을 수 없음 ex) int i = 100; // 100은 리터럴</t>
+  </si>
+  <si>
+    <t>(2) 상수 : 변수가 저장하고있는 값을 수정할수 없게 막고있는것 ex) const int i = 100; 100은 리터럴, i는 상수</t>
+  </si>
+  <si>
+    <t>(3) 결론: 상수의 본질은 변수</t>
+  </si>
+  <si>
+    <t>(1)코드의 유지보수가 쉽다(예 : 리터럴을 여러번 써야하는 상황인데 그값을 바꿔야할때, 리터럴은 일일이 바꿔야 하지만 기호상수를 쓰면 해당값만 바꾸면 한꺼번에 바꿀수 있다.)</t>
+  </si>
+  <si>
+    <t>(2)의미있는 이름을 쓸 수 있다(예 : 리터럴로 15만 적어두면 의미를 파악하기 어렵지만 const int age = 15 는 age가 나이라는 것을 한눈에 파악 할 수있다)</t>
+  </si>
+  <si>
+    <t>6. 리터럴과 상수의 차이점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7. 리터럴대신 기호상수를 쓰는 이유 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)const char *p; //const가 자료형 앞에 붙을경우 참조하고있는 데이터가 상수화됨 따라서 데이터를 바꾸는건 불가능 하지만 포인터 변수 자체값은 바꿀수 있다. 따라서 참조위치를 바꿀 수 있다.</t>
+  </si>
+  <si>
+    <t>(2)char * const q; //const가 포인터변수명 앞에 올경우, 포인터 변수의 값이 상수화 됨 즉 참조위치를 바꿀수 없다 하지만 포인터가 참조하고 있는 데이터는 변경 가능하다.</t>
+  </si>
+  <si>
+    <t>(3)char s[] = "Barking dogs seldom bite.";</t>
+  </si>
+  <si>
+    <t>char t[] = "A bad workman blames his tools";</t>
+  </si>
+  <si>
+    <t>const char* p = s;</t>
+  </si>
+  <si>
+    <t>char* const q  = s;</t>
+  </si>
+  <si>
+    <t>//p[3] = 'a';</t>
+  </si>
+  <si>
+    <t>p = t;</t>
+  </si>
+  <si>
+    <t>q[3] = 'a';</t>
+  </si>
+  <si>
+    <t>//q = t;</t>
+  </si>
+  <si>
+    <t>(1)의미 : 배열의 요소자료형이 포인터인 배열</t>
+  </si>
+  <si>
+    <t>(2)예시 : int i, n;</t>
+  </si>
+  <si>
+    <t>char *fruits[] = { //각 요소가 문자열 리터럴을 참조하는 포인터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apple, </t>
+  </si>
+  <si>
+    <t>blueberry,</t>
+  </si>
+  <si>
+    <t>orange,</t>
+  </si>
+  <si>
+    <t>melon</t>
+  </si>
+  <si>
+    <t>n = sizeof(fruits) / sizeof(fruits[0]); //배열의 개수 구하는 공식</t>
+  </si>
+  <si>
+    <t>for (i = 0;i &lt; n;i++) {</t>
+  </si>
+  <si>
+    <t>printf("%s\n", fruits[i]);</t>
+  </si>
+  <si>
+    <t>(3)2차원배열과의 차이점</t>
+  </si>
+  <si>
+    <t>int i, n;</t>
+  </si>
+  <si>
+    <t>char fruits[4][10] = { // stack영역 저장공간 char형 10개짜리 4덩어리 있는 배열</t>
+  </si>
+  <si>
+    <t>apple, //끝문자(\n)포함해서 6문자만 사용되고 4문자는 낭비</t>
+  </si>
+  <si>
+    <t>(2)선언방법(암기할것) : int (* pa) [10]; // int형 요소 10개짜리 배열을 참조하는 포인터 변수 pa선언</t>
+  </si>
+  <si>
+    <t>(1)포인터 배열 : int * p [10];</t>
+  </si>
+  <si>
+    <t>(2)배열 포인터 : int(*p) [10]; // 이해하지말고 암기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)결론 : ()가 있으면 배열포인터 없으면 포인터 배열 </t>
+  </si>
+  <si>
+    <t>(1)의미 : 함수를 참조하는 포인터</t>
+  </si>
+  <si>
+    <t>(2)사용처 : 주로 콜백 메소드(이벤트 메소드)를 설정하는데 쓰인다.</t>
+  </si>
+  <si>
+    <t>(3)함수포인터형 매개변수에는 함수이름을 설정해주면 된다 단, 아무 함수이름이나 설정할 수 는없고 그 함수포인터형의 리턴값자료형과 매개변수 자료형이 일치하는 함수만 설정 할 수있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. 포인터에서의 const : 두종류가 있으므로 주의 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18. 포인터 배열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19. 배열 포인터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20. 포인터 배열과 배열 포인터 선언방법 비교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21. 함수포인터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)증산시 관비 논삼대 ( 증감 산술 시프트 관계 비트 논리 삼항 대입)</t>
+  </si>
+  <si>
+    <t>8. 연산자 우선순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 함수 포인터를 요소로 가지는 배열</t>
+  </si>
+  <si>
+    <t>(2)선언 예 : int (*pf[5]) (int,int); //리턴값이 int형, 매개변수가 int형 2개인 함수 주소를 참조할수 있는 함수포인터가 요소로서 5개 있는 배열</t>
+  </si>
+  <si>
+    <t>22. 함수 포인터 배열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)argument : 값 -&gt; 리터럴</t>
+  </si>
+  <si>
+    <t>(2)parameter : 변수</t>
+  </si>
+  <si>
+    <t>9. argument 와 parameter의 차이점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)좌항보다 우항의 범위가 작을때에만 우항의 자료형이 좌항의 자료형으로 형변환이 된다 </t>
+  </si>
+  <si>
+    <t>(2)좌항보다 우항의 범위가 클때에는 좌항의 자료형이 우항의 자료형으로 형변환 되는게 아니라 좌항의 자료형은 변하지않고, 우항의 자료형이 좌항의 작은 저장공간에 저장 되어야 하므로 데이터 손실의 문제가 생긴다.</t>
+  </si>
+  <si>
+    <t>10. 대입연산자 암시적 형변환 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.함수호출부와 리턴값의 관계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)함수호출부는 그 함수호출이 끝나면 리턴값으로 덮어쓰기가 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.정수형의 다양한 표현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 10진수 : 그냥 숫자값을 적으면 십진수로 취급(예 : 234)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 8진수 : 0을 먼저적고 그다음에 숫자값을 적으면 그숫자값은 팔진수로 취급된다(예 : 010 -&gt; 팔진수 10 -&gt; 십진수 8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3) 2진수 : 0b를 먼저적고 그다음에 숫자값을 적으면 그숫자값은 이진수로 취급된다(예 : 0b1001 -&gt; 2진수 1001 -&gt; 십진수 9)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4) 16진수 : 0x를 먼저적고 그다음에 숫자값을 적으면 그 숫자값은 16진수로 취급된다(예 : 0x10 -&gt; 16진수 10 -&gt; 10진수 16)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)NULL : 0번지 주소값을 의미(널이라 읽지말고 널번지로 읽도록 노력하자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 따라서 NULL은 주소값이기 때문에 기본자료형 변수 공간에 저장이 불가능하다. 즉 NULL번지를 저장할 수 있는 변수는 포인터변수만 가능하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 배열을 참조하는 포인터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)포인터종류별 참조범위 : 예, int a[3] = {1,2,3};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-1) a : 배열명 , 첫번째요소를 한덩어리로 참조한다(첫번째 요소만 참조의 범위에 해당한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-2) &amp;a : 배열전체를 한덩어리로 참조한다.(배열포인터와 자료형이 같다 따라서 배열포인터의 값을 초기화할때 a를 사용하는것보다 &amp;a를 사용하는것이 정확한 방법이다 단, a를 사용해도 된다(대입연산전 자동형변환이 일어나기때문에 a가 배열포인터의 자료형으로 자동변환 된다))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4) (*pa)[i]와 pa[i]의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-1) (*pa)[i] : pa가 int 형 요소 10개짜리 배열을 한덩어리로 참조하는 포인터이므로, (*pa)는 pa가 참조중인 배열 한덩어리를 의미하고 따라서 [i]는 그 배열의 인덱싱을 의미하므로 요소 하나씩 추출 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-2) pa[i] : 여기서의 pa는 배열명과 같은 의미로 사용됬다. 그런데 pa가 참조하는 범위는 int형 요소 10개짜리 배열 한덩어리 이므로 pa[0]이 의미하는건 int형 요소 10개짜리 배열 전체다. 그리고 pa[1]은 그다음의 int형 요소 10개짜리 배열 만큼의 메모리공간을 참조하는 첫번째주소다. 그래서 pa[0]과 pa[1]사이에는 40바이트의 크기차이가 발생하게 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.매크로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) #define 의미 : A를 B로 컴파일전에 바꾸다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)단순 매크로는 기호상수 역할을 한다. 컴파일전에 바꿔치기 한다(예시 : #define Print printf)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.증감연산자 주의점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define SQ(x) ((x) *(x))</t>
+  </si>
+  <si>
+    <t>main() {</t>
+  </si>
+  <si>
+    <t>int x = 2;</t>
+  </si>
+  <si>
+    <t>printf("%d\n", SQ(++x));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)함수 매크로 매개변수가 존재하는 매크로(함수와 매우 유사함 그러나 함수는 아니다) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)함수 매크로 주의사항 : 매개변수의 자료형이 없다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-1)함수매크로의 매개변수를 매크로의 바디에서 정의할떄 괄호를 묶어줘야한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-3)매크로와 이름과 괄호 사이에 공백이 있으면 안된다.(예시 #define ADD (x,y) ((x) + (y))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-2)함수매크로의 매개변수는 바디에서 모두 사용안할시에 에러 발생(예시 : #define ADD(x,y) ((x) *(x))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-4) 매크로의 바디에서 줄바꿈할때 \를 사용한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1-1) 특히 매크로에서 증감연산 사용은 자제한다 나도 모르게 위와같은 Undefined Behaviour상태가 발생할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)같은 증감연산자를 하나의 문장에서 두번이상 사용하면 Undefined Behaviour상태가 된다. 즉 C문법에서 정의되지않는 식이 되므로 사용하지말것(컴파일러마다 다르게 값이 나올 수 있다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(3-5)문자열 변환연산자(#) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define PRINT(exp) printf(#exp" =%d\n",exp) //문자열안에는 치환대상에 포함이 안된다. 매크로 #연산자는 교과서 610페이지 참조</t>
+  </si>
+  <si>
+    <t>int x = 5;</t>
+  </si>
+  <si>
+    <t>PRINT(x);</t>
+  </si>
+  <si>
+    <t>(3-6)내장매크로 라이브러리에서 기본으로 제공해주는 매크로다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-7)내장메크로 종류 : __DATE__ (%s로 출력,컴파일된 날짜(월, 일, 년)으로 치환된다) __TIME__ (%s로 출력, 컴파일된 시간(시,분,초)로 치환) __LINE__ (%d로 출력, 현재의 라인번호로 치환) __FILE__ (%s로 출력, 소스파일 이름으로 치환)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.exit() 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-8)ASSERT 매크로 : 코드의 특정위치에서 어떤변수값이 내가 예상한값이랑 같은지 다른지 체크하는 용도 (교제 612페이지 참조)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-9)함수와 함수매크로의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-10)함수매크로는 함수보다 빠른 작업속도를 가지지만, 코드를 2~3줄 이상으로 길게쓰면 복잡해지기 때문에 길게 쓰기힘들다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ifdef 매크로이름</t>
+  </si>
+  <si>
+    <t>#else</t>
+  </si>
+  <si>
+    <t>1. 조건부 컴파일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1. #if ~ #else ~ #endif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1-2. #ifdef ~ #else ~ #endif </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 앞에 #define으로 매크로가 정의 되어있으면 참, 매크로가 정의되어있지 않으면 거짓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)사용법 예시 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 사용법 예시:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3. #ifndef ~ #else ~ #endif </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : #ifdef와 반대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ifndef LIMIT</t>
+  </si>
+  <si>
+    <t>#define LIMIT 1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3-11)매크로취소 #undef : #define으로 정의한 매크로를 취소 시킨다. 예 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define SIZE 100</t>
+  </si>
+  <si>
+    <t>#undef SIZE</t>
+  </si>
+  <si>
+    <t>#define METHOD 1</t>
+  </si>
+  <si>
+    <t>#if METHOD == 1</t>
+  </si>
+  <si>
+    <t>printf("1");</t>
+  </si>
+  <si>
+    <t>(1)의미 : #if다음에는 조건식(조건식에는 정수,다른 매크로만 비교가 가능하다(실수,캐릭터형 X))이 오고 그조건식에서는 매크로에 대한 수식이여야 한다. 그리고 그 결과가 참 아니면 거짓으로 나온다 조건이 참일때 바디가 컴파일할때 포함이 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.defined(매크로이름)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 매개변수로 받은 매크로가 정의 되어있는지 아닌지 0,1로 리턴한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.sizeof()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)주의사항 : 전처리기의 조건식에서만 쓰일 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)예시 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)예시 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#if defined(METHOD)</t>
+  </si>
+  <si>
+    <t>(1)의미: 매개변수의 크기를 unsigned long long으로 리턴해주는 연산자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 예시 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sizeof(int);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)주석처리 용도 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#if 0</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>4. #include &lt;헤더파일 이름&gt;, #include "헤더파일 이름"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 컴파일전에 헤더파일을 소스코드에 포함시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) &lt;&gt;와 ""의 차이 : &lt;&gt;는 이컴퓨터에 설치 되어 있는 내가 아닌 다른사람이 작성한 헤더파일을 포함시킬때(C표준 라이브러리 또는 window API등등), ""는 내가 만든 헤더파일을 포함시킬때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)주의사항 : ""쓸때에는 헤더파일이 존재하는 경로까지 적어야하는데 현재작성하는 소스코드랑 같은 폴더에 있으면 경로는 생략 가능하다. 그래서 일반적으로 내가 만든 헤더파일은 소스코드와 같은 폴더에 저장 시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.실행파일이 만들어 지는 과정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ex ) _getch</t>
-  </si>
-  <si>
-    <t>6. gets</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. fgets()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 조건부 컴파일(조건식이 참일때만 컴파일한다 따라서 조건식이 거짓이면 안에있는게 컴파일이 안된다 이특성을 이용하여 주석으로 이용할 수 있다.)</t>
-  </si>
-  <si>
-    <t>(2) 사용법 예시: #if 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         printf("ez");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         #endif</t>
-  </si>
-  <si>
-    <t>1. #if #endif</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. buffer 함수인지 아닌지 판별하는 법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 운영체제가 하는일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. EOF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. 문자인코딩 방식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)세세하지않고 일반적으로 뭉뚱그려서 비교하면 ASCII코드 방식과 UNI코드 방식으로 나뉜다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(3)ASCII코드 : ansi에서 만든 문자 하나당 1바이트 공간을 할당 하는 인코딩 방식 8비트중에 7비트만 문자 데이터 저장용으로 사용하고 1비트는 에러체크용 총 128(7비트)개의 문자의 코드값을 부여함.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ansi에서 만들었기 때문에 미국 국내용으로 만들어진 코드다. 따라서 영어위주로 만들어져있다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)ansi : 미국 국가표준 협회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(4)ansi 코드 : ansi에서 ASCII코드를 확장해서 만든 인코딩방식 에러비트를 없애서 8비트 모두 문자 코드값이 부여됨 총 256(8비트)문자에 대한 코드값이 부여. 미국 국내용으로 만들었음.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MS에서 O/S나 응용프로그램을 만들때 문자인코딩방식으로 ansi 코드를 사용함. Python에서도 기본 인코딩 방식이 ansi코드다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예를 들어서, 메모장(default 인코딩 설정값이 utf-8)에서 쓴 내용을 Python(default 디코딩 설정값이 ansi)에서 불러오려면 저장할때 ansi로 맞춰서 저장하거나, Python 함수의 기본 디코딩 방식을 utf-8로 설정해야 한다. Default 옵션쓰면 디코딩방식이 다르기 때문에 에러남.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5)CP949코드 : MS에서 만든 한국어 지원 ansi 확장코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>만약 컴퓨터에 설치되어 있는 윈도우가 영어판 윈도우면 거기서 사용하는 문자 인코딩,디코딩방식은 ansi코드를 쓴다. 만약 윈도우가 한글판이면 ansi코드중에서 CP949를 씀.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예 : 만약 윈도우가 중국어판 윈도우면 문자 인코딩,디코딩 방식으로 ansi확장판으로 cp936등이 사용된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(7)에러처리 방식 : 문자데이터와 별개의 비트를 추가해서 그비트를 이용해서 에러 정보를 교환한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6)utf-8 : 가장 많이 사용하는 UNI코드다. 영어문자(ASCII코드에 있는 문자)는 1바이트(ASCII코드)를 쓰고, 비영어권 문자는 2바이트(UNI 코드)를 쓴다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 컴파일전에 처리 되는 코드</t>
-  </si>
-  <si>
-    <t>(2)위치: 어디든지 상관없다 메인안이여도 처리된다.</t>
-  </si>
-  <si>
-    <t>2. 전처리기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 그 함수가 정의되어 있지 않다.</t>
-  </si>
-  <si>
-    <t>(2)해결법 : 오타가 있는지 찾아본다. 또는 #include를 했는지 확인 또는 함수가 퇴출당했는지 찾아본다.</t>
-  </si>
-  <si>
-    <t>1. 에러 싸인 종류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#include &lt;stdio.h&gt;</t>
-  </si>
-  <si>
-    <t>int CW(char* s); //함수원형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">main() </t>
-  </si>
-  <si>
-    <t>int wc = CW("the c book"); //함수호출</t>
-  </si>
-  <si>
-    <t>printf("%d", wc); //값출력</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int CW(char* s) </t>
-  </si>
-  <si>
-    <t>int i, wc = 0, waitung = 1; //변수 선언과 초기화</t>
-  </si>
-  <si>
-    <t>for (i = 0;s[i] != NULL; ++i) //조건식 : i를 0으로 초기화, 배열의 i인덱스가 null이 아닐때(문장끝인지 아닌지 판별 '\0'=0=NULL=문자열의 끝 ), i +1추가</t>
-  </si>
-  <si>
-    <t>if (isalpha(s[i])) //포인터 s가 참조하는 데이터 영역의 문자열 리터럴(the c book)의 i번째 요소가 알파벳인지 체크</t>
-  </si>
-  <si>
-    <t>if (waitung) //waitung이 0이 아닌 값일때만 바디실행</t>
-  </si>
-  <si>
-    <t>wc++; //wc값(단어의 개수) 1증가</t>
-  </si>
-  <si>
-    <t>waitung = 0; //waitung값 0으로 초기화</t>
-  </si>
-  <si>
-    <t>else  //포인터 s가 참조하는 데이터 영역의 문자열 리터럴이 알파벳이 아닐때 바디실행</t>
-  </si>
-  <si>
-    <t>waitung = 1; //waitung값 1로 초기화</t>
-  </si>
-  <si>
-    <t>return wc; //for문이 끝나고 최종적으로 체크가 끝난 wc(단어의 개수)를 뱉어냄</t>
-  </si>
-  <si>
-    <t>1. 문자열에서 단어 개수 세는 알고리즘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) #define 의미 : A를 B로 컴파일전에 바꾸다</t>
-  </si>
-  <si>
-    <t>(2) typedef 의미 : 새로운 자료형 정의 a와 같은자료형을 b라는 이름으로 '새로운' 자료형을 만들어 낸다(a는 그대로 보존,b가 새로 생성) ex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2-2)typedef 사용이유 : 자료형의 이름으로 그 변수가 무슨 의미인지 파악하기 쉽고, 플랫폼이 다른경우 소스코드를 따로 적어야하지만 typedef를 사용함으로써 플랫폼에 알맞는 자료형이 자동으로 </t>
-  </si>
-  <si>
-    <t>사용되도록 만들 수 있다 (#if 사용)</t>
-  </si>
-  <si>
-    <t>(2-3) typedef 기존자료형이름 새로 만들 자료형이름</t>
-  </si>
-  <si>
-    <t>#ifdef _WIN64 //윈도우 64비트가 깔려있는 컴퓨터</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef unsigned __int64 size_t; //64비트용 정수 자료형이 size_t로 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef __int64          ptrdiff_t;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef __int64          intptr_t;</t>
-  </si>
-  <si>
-    <t>#else // O/S가 64비트가 아니라면</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef unsigned int     size_t; //일반정수자료형(부호가없는)이 size_t로 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef int              ptrdiff_t;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    typedef int              intptr_t;</t>
-  </si>
-  <si>
-    <t>#endif</t>
-  </si>
-  <si>
-    <t>(3) 차이점 :#define은 a를 b로 대체하는 것이고(자료형 x) typedef는 a는 보존한채 b라는 새로운 자료형 창조</t>
-  </si>
-  <si>
-    <t>3. #define과 typedef</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)dst = destination (목적지)</t>
-  </si>
-  <si>
-    <t>(2)src = source (원본)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)cat = concatenate (연결한다) </t>
-  </si>
-  <si>
-    <t>(3-2) 예시 : "hi" + " Tom"</t>
-  </si>
-  <si>
-    <t>-&gt; "hi Tom"</t>
-  </si>
-  <si>
-    <t>(4)cmp = compare (비교하다)</t>
-  </si>
-  <si>
-    <t>(5)chr = character (문자)</t>
-  </si>
-  <si>
-    <t>(6)loc = location (위치)</t>
-  </si>
-  <si>
-    <t>3. 많이 쓰이는 매개변수명 목록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) Solution Explore -&gt; 프로젝트 이름 -&gt; 우클릭 -&gt; Properties -&gt; General -&gt; SDL checks </t>
-  </si>
-  <si>
-    <t>1. SDL 체크 해제 하는법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PID : prcess ID (운영체제가 프로세스를 식별하기 위해 부여한 식별번호)</t>
-  </si>
-  <si>
-    <t>4. process : 실행중인 프로그램을 프로세스라 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆儆4?쇌</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
-    <t>Press any key to close this window . . .</t>
-  </si>
-  <si>
-    <t>unresolved external symbol ~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C:\Users\USER\source\repos\Project62\x64\Debug\Project62.exe (process 5432) exited with code 0.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)해결법 :</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 정상적으로 프로그램이 실행되고 끝났다는 의미 하지만 원하는 방식으로 프로그램이 처리된게 아닐수도 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) A + B로 연결, concatenate기능을 함수로 구현</t>
-  </si>
-  <si>
-    <t>(2)예시 : char dst[12] = "hello";</t>
-  </si>
-  <si>
-    <t>char src[7] = " world";</t>
-  </si>
-  <si>
-    <t>strcat(dst, src);</t>
-  </si>
-  <si>
-    <t>printf("%s", dst);</t>
-  </si>
-  <si>
-    <t>(1) 의미 : 토큰은 문법적으로 더이상 나눌수 없는 기본적인 요소(공백으로 분리된 단어각각을 의미) 예시 "I am a boy" //여기서 토큰은 "I","am","a","boy" 4개로 존재</t>
-  </si>
-  <si>
-    <t>(1)atoi : str을 int형으로 변환한다</t>
-  </si>
-  <si>
-    <t>(2)atof : str을 double형으로 변환한다.</t>
-  </si>
-  <si>
-    <t>(3) 예시</t>
-  </si>
-  <si>
-    <t>5. strcat(A, B)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. token</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. atoi, atof 함수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)컴파일할때 실행파일의 헤더에 메인함수의 주소 위치정보가 같이 포함된채로 exe가 완성된다.</t>
-  </si>
-  <si>
-    <t>(2)exe를 실행하면 O/S가 메모리에 코드영역에서 메인함수의 위치정보를 알아내서 메인함수 호출</t>
-  </si>
-  <si>
-    <t>(3)STACK영역에 메인함수의 바디 데이터가 저장되고 O/S는 그 데이터를 보고 프로세스 진행</t>
-  </si>
-  <si>
-    <t>5. main()함수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미: continue를 만나면 for문에선 증감식, while문에서는 조건식으로 간다.</t>
-  </si>
-  <si>
-    <t>1. continue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11. 함수에서 선언된 포인터형 변수(지역변수)를 리턴하면 안된다 왜냐하면 함수종료후에 포인터형 변수가 참조하고 있는 주소위치의 데이터가 운영체제의 의해 삭제되기 때문이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. strlen()함수 유의사항 : 널문자는 개수에 포함을 안시키기 때문에 for문에서 두번째 조건식에 strlen 함수사용시 조심해야 한다. 문자배열에 요소하나씩 대입시킬때 널문자를 반드시 포함시켜줘야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)포인터형으로 리턴한다(배열형으로 리턴하는건 문법에러)</t>
-  </si>
-  <si>
-    <t>(2)함수에서 리턴하지말고 call by reference를 활용하여 원본 또는 caller에서 수정될 배열을 선언하고 그 배열을 함수로 전달받아서 수정한다.</t>
-  </si>
-  <si>
-    <t>12. 함수에서 배열리턴해야할때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)정의 : struct tag이름 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 바디(함수는 바디에 포함 안됨)</t>
-  </si>
-  <si>
-    <t>}; // 정의와 동시에 구조체 변수 선언은 C언어 책521P 참고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)변수선언 : (1)에서 구조체를 정의한후 struct tag x; </t>
-  </si>
-  <si>
-    <t>(3)구조체는 생김새는 클래스와 비슷하지만, 기본자료형이다. 참조변수X</t>
-  </si>
-  <si>
-    <t>(4)구조체 멤버변수로 포인터를 가지고있을때 초기화를 안해두면 default값으로 NULL이 된다.</t>
-  </si>
-  <si>
-    <t>1. 구조체(struct)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) int* p;</t>
-  </si>
-  <si>
-    <t>int x = 7;</t>
-  </si>
-  <si>
-    <t>p = &amp;x;</t>
-  </si>
-  <si>
-    <t>ex) int x = 7;</t>
-  </si>
-  <si>
-    <t>int y;</t>
-  </si>
-  <si>
-    <t>y = x; //깊은복사의 예</t>
-  </si>
-  <si>
-    <t>13.얕은 복사 : 주소값만 복사 얕은복사는 =으로 구현함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14. 깊은 복사 : 데이터를 복사 깊은복사는 보통 함수를 제공함(ex) strcpy())</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p.구조체멤버변수이름; //에러남</t>
-  </si>
-  <si>
-    <t>15. 간접참조 연산자(*)를 사용하는경우 : (*p).구조체 멤버변수이름; // ()치는 이유 : .연산자가 *보다 연산자 우선순위가 빠르기 때문이다. 따라서 *p.구조체 멤벼변수를 쓰면 p.구조체멤버변수로 처리되고 그이후 *이 따로 처리된다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16. 간접멤버연산자(-&gt;)를 사용하는경우 : p-&gt;구조체 멤버변수이름;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)double이 float보다 정확하다.</t>
-  </si>
-  <si>
-    <t>1. float과 double</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)메모리 크기 : 공용체는 풀워드단위(하프워드 : 2바이트 풀워드 : 4바이트 더블워드 : 8바이트)로 끊기때문에 4바이트씩 끊어져야한다</t>
-  </si>
-  <si>
-    <t>2. 공용체(union)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 메모리 크기 : 4바이트(내부적으로는 정수형으로 처리된다)</t>
-  </si>
-  <si>
-    <t>(2)사용처 : 예측할 수 없는 값의 입력을 방지하기위해서 enum을 사용한다. 그리고 enum의 요소값으로 의미있는 상수이름을 부여함으로써 상수값지정할때 혼동을 방지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3) 예시 : </t>
-  </si>
-  <si>
-    <t>2. enum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)주의사항 : math.h에 함수원형이 저장되어 있다.</t>
-  </si>
-  <si>
-    <t>1. abs() (절댓값을 리턴해주는 함수)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>struct food a[] = {</t>
-  </si>
-  <si>
-    <t>{"bubble gum",1000}</t>
-  </si>
-  <si>
-    <t>};</t>
-  </si>
-  <si>
-    <t>printf("%s %d",a[0].name,a[0].c);</t>
-  </si>
-  <si>
-    <t>(1)struct food a[2];</t>
-  </si>
-  <si>
-    <t>a-&gt;c = 1000; //첫번째 요소</t>
-  </si>
-  <si>
-    <t>strcpy(a-&gt;name, "kimch");</t>
-  </si>
-  <si>
-    <t>(a + 1)-&gt;c = 2000; //두번째 요소</t>
-  </si>
-  <si>
-    <t>strcpy((a + 1)-&gt;name, "gum");</t>
-  </si>
-  <si>
-    <t>printf("%s %d",(a+1)-&gt;name,(a+1)-&gt;c);</t>
-  </si>
-  <si>
-    <t>3. 배열 .연사자를 이용한 표기법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. 구조체 배열에서 요소값을 포인터방식으로 설정하는 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 리터럴 : 값(데이터)가 저장되는 공간 항상 데이터 영역에 존재함 다른값을 대입받을 수 없음 ex) int i = 100; // 100은 리터럴</t>
-  </si>
-  <si>
-    <t>(2) 상수 : 변수가 저장하고있는 값을 수정할수 없게 막고있는것 ex) const int i = 100; 100은 리터럴, i는 상수</t>
-  </si>
-  <si>
-    <t>(3) 결론: 상수의 본질은 변수</t>
-  </si>
-  <si>
-    <t>(1)코드의 유지보수가 쉽다(예 : 리터럴을 여러번 써야하는 상황인데 그값을 바꿔야할때, 리터럴은 일일이 바꿔야 하지만 기호상수를 쓰면 해당값만 바꾸면 한꺼번에 바꿀수 있다.)</t>
-  </si>
-  <si>
-    <t>(2)의미있는 이름을 쓸 수 있다(예 : 리터럴로 15만 적어두면 의미를 파악하기 어렵지만 const int age = 15 는 age가 나이라는 것을 한눈에 파악 할 수있다)</t>
-  </si>
-  <si>
-    <t>6. 리터럴과 상수의 차이점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">7. 리터럴대신 기호상수를 쓰는 이유 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)const char *p; //const가 자료형 앞에 붙을경우 참조하고있는 데이터가 상수화됨 따라서 데이터를 바꾸는건 불가능 하지만 포인터 변수 자체값은 바꿀수 있다. 따라서 참조위치를 바꿀 수 있다.</t>
-  </si>
-  <si>
-    <t>(2)char * const q; //const가 포인터변수명 앞에 올경우, 포인터 변수의 값이 상수화 됨 즉 참조위치를 바꿀수 없다 하지만 포인터가 참조하고 있는 데이터는 변경 가능하다.</t>
-  </si>
-  <si>
-    <t>(3)char s[] = "Barking dogs seldom bite.";</t>
-  </si>
-  <si>
-    <t>char t[] = "A bad workman blames his tools";</t>
-  </si>
-  <si>
-    <t>const char* p = s;</t>
-  </si>
-  <si>
-    <t>char* const q  = s;</t>
-  </si>
-  <si>
-    <t>//p[3] = 'a';</t>
-  </si>
-  <si>
-    <t>p = t;</t>
-  </si>
-  <si>
-    <t>q[3] = 'a';</t>
-  </si>
-  <si>
-    <t>//q = t;</t>
-  </si>
-  <si>
-    <t>(1)의미 : 배열의 요소자료형이 포인터인 배열</t>
-  </si>
-  <si>
-    <t>(2)예시 : int i, n;</t>
-  </si>
-  <si>
-    <t>char *fruits[] = { //각 요소가 문자열 리터럴을 참조하는 포인터</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apple, </t>
-  </si>
-  <si>
-    <t>blueberry,</t>
-  </si>
-  <si>
-    <t>orange,</t>
-  </si>
-  <si>
-    <t>melon</t>
-  </si>
-  <si>
-    <t>n = sizeof(fruits) / sizeof(fruits[0]); //배열의 개수 구하는 공식</t>
-  </si>
-  <si>
-    <t>for (i = 0;i &lt; n;i++) {</t>
-  </si>
-  <si>
-    <t>printf("%s\n", fruits[i]);</t>
-  </si>
-  <si>
-    <t>(3)2차원배열과의 차이점</t>
-  </si>
-  <si>
-    <t>int i, n;</t>
-  </si>
-  <si>
-    <t>char fruits[4][10] = { // stack영역 저장공간 char형 10개짜리 4덩어리 있는 배열</t>
-  </si>
-  <si>
-    <t>apple, //끝문자(\n)포함해서 6문자만 사용되고 4문자는 낭비</t>
-  </si>
-  <si>
-    <t>(1)의미 : 배열을 참조하는 포인터</t>
-  </si>
-  <si>
-    <t>(2)선언방법(암기할것) : int (* pa) [10]; // int형 요소 10개짜리 배열을 참조하는 포인터 변수 pa선언</t>
-  </si>
-  <si>
-    <t>(1)포인터 배열 : int * p [10];</t>
-  </si>
-  <si>
-    <t>(2)배열 포인터 : int(*p) [10]; // 이해하지말고 암기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)결론 : ()가 있으면 배열포인터 없으면 포인터 배열 </t>
-  </si>
-  <si>
-    <t>(1)의미 : 함수를 참조하는 포인터</t>
-  </si>
-  <si>
-    <t>(2)사용처 : 주로 콜백 메소드(이벤트 메소드)를 설정하는데 쓰인다.</t>
-  </si>
-  <si>
-    <t>(3)함수포인터형 매개변수에는 함수이름을 설정해주면 된다 단, 아무 함수이름이나 설정할 수 는없고 그 함수포인터형의 리턴값자료형과 매개변수 자료형이 일치하는 함수만 설정 할 수있다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. 포인터에서의 const : 두종류가 있으므로 주의 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18. 포인터 배열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19. 배열 포인터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20. 포인터 배열과 배열 포인터 선언방법 비교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21. 함수포인터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)증산시 관비 논삼대 ( 증감 산술 시프트 관계 비트 논리 삼항 대입)</t>
-  </si>
-  <si>
-    <t>8. 연산자 우선순위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 함수 포인터를 요소로 가지는 배열</t>
-  </si>
-  <si>
-    <t>(2)선언 예 : int (*pf[5]) (int,int); //리턴값이 int형, 매개변수가 int형 2개인 함수 주소를 참조할수 있는 함수포인터가 요소로서 5개 있는 배열</t>
-  </si>
-  <si>
-    <t>22. 함수 포인터 배열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)argument : 값 -&gt; 리터럴</t>
-  </si>
-  <si>
-    <t>(2)parameter : 변수</t>
-  </si>
-  <si>
-    <t>9. argument 와 parameter의 차이점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)좌항보다 우항의 범위가 작을때에만 우항의 자료형이 좌항의 자료형으로 형변환이 된다 </t>
-  </si>
-  <si>
-    <t>(2)좌항보다 우항의 범위가 클때에는 좌항의 자료형이 우항의 자료형으로 형변환 되는게 아니라 좌항의 자료형은 변하지않고, 우항의 자료형이 좌항의 작은 저장공간에 저장 되어야 하므로 데이터 손실의 문제가 생긴다.</t>
-  </si>
-  <si>
-    <t>10. 대입연산자 암시적 형변환 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex ) getchar scanf호출후에 getchar를 쓰게되면 scanf에 대한 변수 입력값이 enter키('\n')가 버퍼에 들어가고 그 문자가 getchar에 의해서 읽히게 되어서 기다리지 않고 다음줄로 넘어가게된다 따라서 getchar써서 실행을 중지시키고자 한다면 getchar를 두번쓰던가 아래에 있는 _getch를 쓰면 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.헤더파일의 구성물 : 함수원형,구조체 선언,#typedef,#define</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-1)주의사항 : 같은함수원형이 두번 반복되면 문법적으로 문제가 없다 하지만 헤더파일안에 구조체 선언이 되어있다면 헤더파일이 중복적으로 포함되면 안된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.정적할당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)상대주소 : 특정 영역내에 주소(컴파일전에 배정) // 절대주소 : 메모리의 원래 주소(고정되있다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)정적할당 : 컴파일 타임에서 메모리의 상대주소값이 결정되는 것을 말한다. 램의 data영역과 stack영역이 여기에 해당된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.동적할당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)런타임에 메모리의 주소값과 크기가 결정되는 것을 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)주의 : 정적할당 문법을 사용하여 메모리의 크기를 변경시키는것은 불가능하다 (예: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int size = 200;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int score_s[size]; //상황에 따라 사이즈값을 변경하려고 시도하기위해 코딩을 할 수도있는데 컴파일에러가 발생함 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name = (char*)malloc(sizeof(char) * 100); /*명시적 형변환을 한이유는 malloc 함수가 보이드 포인터형으로 리턴하기 때문이다. sizeof를 사용한 이유는 float,long같은자료형은 CPU,운영체제에 따라서 사이즈가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)할당을 받은후에는 할당이 안된 버그나 그런걸 방지하기 위해 널체크를 해준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char* s1 = (char*)malloc(sizeof(char) * 100); //malloc() 함수에서 동적 메모리 할당에 실패하면 NULL을 반환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)프로그램을 강제로 종료시키는 함수 매개변수의 의미는 에러코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4.실행파일의 비트값(32비트용 또는 64비트)은 개발자(이실행파일을 컴파일한)컴퓨터의 시스템 비트값의 의해 결정된다 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예를들어 개발자컴퓨터에 64비트용 윈도우가 설치되어있으면 그컴퓨터로 컴파일한 파일에는 #define _WIN64가 자동포함(컴파일러)된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만약에 개발자컴퓨터가 32비트용 윈도우라면 #define _WIN64가 포함되지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-1)사용자의 컴퓨터가 32비트 윈도우가 설치되어 있다면 오동작할 수 있다. 그래서 애초에 32비트 윈도우에서 64비트 프로그램을 다운로드받은것 자체가 잘못이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-2)사용자의 컴퓨터가 64비트 윈도우가 설치되어 있다면 실행파일도 64비트용으로 정의되어 있기 때문에 아무문제 없이 동작한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만약에 개발자의 컴퓨터에 32비트 운영체제가 설치되어 있다면, 컴파일과정에서 실행파일에 #define _WIN64가 포함되지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-3)사용자의 컴퓨터가 32비트용 윈도우라면 실행파일에 아무문제 없이 정상작동한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-4)사용자의 컴퓨터가 64비트 윈도우라면 실행파일이 32비트용이라 하더라도 메모리공간이 부족할일이 없기 때문에 아무 문제 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)calloc(size_t n, size_t size) //첫번째매개변수는 요소의 개수 두번째 매개변수는 요소의 크기 동적할당을 한후 각요소값이 0으로 초기화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)malloc(size_t a) //a = calloc함수의 n * size와 같다. 동적할당한후 요소의 값이 쓰레기값이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.malloc(), calloc(),realloc()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)realloc(void * b,size_t c) // b는 기존 동적메모리 크키(참조변수),c는 요소의 크기다 앞에 할당받은 자료형만 같고 새로운 공간을 할당받는다(기존공간유지 따라서 기존공간도 나중에 free()해줘야 한다) 동적할당후 쓰레기값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-1)double* new_array = realloc(scores, new_limit * sizeof(double)); // 첫번째 매개변수가 NULL이면 malloc과 같다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1111,7 +1499,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1130,6 +1521,148 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>53341</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>78009</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60AD415F-676A-BE19-9930-711A30B256FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7566661"/>
+          <a:ext cx="2971800" cy="1571528"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>313212</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>213945</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39DB2A94-5FB4-7AF7-24DD-3D744D729490}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="220980"/>
+          <a:ext cx="5677692" cy="4191585"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>220979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>175220</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FC01244-3F1A-CC3F-AB03-4A91FD27BF76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="4861559"/>
+          <a:ext cx="5699759" cy="2826981"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1429,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1724AF87-E043-4ABE-83D5-9A45F460A764}">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.796875" customWidth="1"/>
@@ -1562,7 +2095,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
@@ -1582,27 +2115,27 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>55</v>
+        <v>396</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -1612,487 +2145,800 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>84</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>86</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>87</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>88</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B68" t="s">
-        <v>77</v>
+      <c r="A68" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C69" t="s">
-        <v>78</v>
+      <c r="B69" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C70" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A71" t="s">
-        <v>75</v>
+      <c r="C71" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
-        <v>82</v>
+      <c r="A74" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B75" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A78" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>218</v>
+      <c r="B76" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A85" t="s">
-        <v>232</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B87" t="s">
-        <v>227</v>
+      <c r="A87" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B88" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>233</v>
+      <c r="B89" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B91" t="s">
-        <v>230</v>
+      <c r="A91" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B92" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
-        <v>235</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B93" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>298</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B103" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B105" t="s">
-        <v>270</v>
+      <c r="A103" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B104" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B106" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B108" t="s">
-        <v>272</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B107" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B109" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B111" t="s">
-        <v>274</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B110" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B112" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
-        <v>299</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B113" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B117" t="s">
-        <v>278</v>
+      <c r="A117" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C118" t="s">
-        <v>279</v>
+      <c r="B118" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C119" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C120" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C121" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B122" t="s">
-        <v>249</v>
+      <c r="C122" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B123" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B124" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C125" t="s">
-        <v>285</v>
+      <c r="B125" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B126" t="s">
+      <c r="C126" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B127" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B129" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C130" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B130" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C131" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C132" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C133" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B134" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C134" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B135" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B136" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C137" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B138" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B137" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C138" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B139" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A144" t="s">
-        <v>301</v>
-      </c>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A144" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>294</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>297</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>306</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>412</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A144:E144"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5739C7DF-469D-4675-A9EA-9348728B670E}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>393</v>
+      </c>
+      <c r="I41" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="I42" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>407</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD9762D-2504-49A1-9223-9FCF6FA6F21B}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -2101,34 +2947,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA55DE28-1A94-43AE-AB21-14ECD2B4728D}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
@@ -2138,27 +2984,27 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2167,29 +3013,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA6A7E4-F2A8-4E2F-9D3C-4F7B0A25993B}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -2199,12 +3045,12 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -2214,7 +3060,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
@@ -2224,12 +3070,12 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
@@ -2239,7 +3085,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
@@ -2249,7 +3095,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
@@ -2259,12 +3105,12 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E24" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
@@ -2279,7 +3125,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
@@ -2289,7 +3135,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
@@ -2304,7 +3150,7 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
@@ -2325,32 +3171,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2361,17 +3207,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CE440D-3B83-4706-A59E-8672DC456340}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -2387,12 +3278,12 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -2402,97 +3293,97 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -2623,87 +3514,87 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -2713,47 +3604,47 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>384</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
@@ -2768,135 +3659,135 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="N72" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B81" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B82" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B83" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2907,7 +3798,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3EF0EA-AD2F-4FD9-A6AF-267B4D26F4BF}">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -2922,177 +3813,178 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>312</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3103,12 +3995,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3124,12 +4016,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3140,127 +4032,388 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4CCDE3-1A5A-486E-96E8-485C742A1D39}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>174</v>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B69" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B70" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H78" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>379</v>
+      </c>
+      <c r="H79" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/C언어_필기.xlsx
+++ b/C언어_필기.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4690C12F-5C19-4421-99C0-C0F7A8524AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A0022A-893D-4591-B71F-78E6EF0D5835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
   </bookViews>
   <sheets>
     <sheet name="포인터" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="434">
   <si>
     <t>(1)의미 : 주소값을 저장하는 메모리 공간</t>
   </si>
@@ -1453,6 +1453,72 @@
   </si>
   <si>
     <t>(3-1)double* new_array = realloc(scores, new_limit * sizeof(double)); // 첫번째 매개변수가 NULL이면 malloc과 같다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9.scanf() 함수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)예시코드 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int x, y, z;</t>
+  </si>
+  <si>
+    <t>int* px, * py, * pz, * tmp;</t>
+  </si>
+  <si>
+    <t>px = &amp;x;</t>
+  </si>
+  <si>
+    <t>py = &amp;y;</t>
+  </si>
+  <si>
+    <t>pz = &amp;z;</t>
+  </si>
+  <si>
+    <t>scanf("%d", px); // scanf의 기능은 첫번째 매개변수의 형식대로 입력을 하면 두번째 매개변수의 주소공간에 입력한 값을 저장(px에 참조하고 있는 x에 저장)</t>
+  </si>
+  <si>
+    <t>scanf("%d", py);</t>
+  </si>
+  <si>
+    <t>scanf("%d", pz);</t>
+  </si>
+  <si>
+    <t>//printf("%d", *px);</t>
+  </si>
+  <si>
+    <t>/*tmp = py;</t>
+  </si>
+  <si>
+    <t>py = px;</t>
+  </si>
+  <si>
+    <t>px = tmp;</t>
+  </si>
+  <si>
+    <t>tmp = pz;</t>
+  </si>
+  <si>
+    <t>pz = px;</t>
+  </si>
+  <si>
+    <t>px = tmp;*/</t>
+  </si>
+  <si>
+    <t>tmp = py;</t>
+  </si>
+  <si>
+    <t>px = pz;</t>
+  </si>
+  <si>
+    <t>printf("%d %d %d", *px, *py, *pz);</t>
+  </si>
+  <si>
+    <t>(1)의미 : scanf의 기능은 첫번째 매개변수의 형식대로 입력을 하면 두번째 매개변수의 주소공간에 입력한 값을 저장(px가 참조하고 있는 x에 저장)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3394,7 +3460,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53EDAC2-69D8-41B7-8499-C3945599E82E}">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3788,6 +3854,114 @@
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>414</v>
+      </c>
+      <c r="C98" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C99" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C101" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C102" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C103" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C105" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C106" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C108" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C110" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C111" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C112" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C113" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C114" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C115" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C117" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C118" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C119" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C122" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/C언어_필기.xlsx
+++ b/C언어_필기.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A0022A-893D-4591-B71F-78E6EF0D5835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4690C12F-5C19-4421-99C0-C0F7A8524AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{93A6D704-CBC4-4F85-B6A2-0780959A0C65}"/>
   </bookViews>
   <sheets>
     <sheet name="포인터" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="413">
   <si>
     <t>(1)의미 : 주소값을 저장하는 메모리 공간</t>
   </si>
@@ -1453,72 +1453,6 @@
   </si>
   <si>
     <t>(3-1)double* new_array = realloc(scores, new_limit * sizeof(double)); // 첫번째 매개변수가 NULL이면 malloc과 같다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">9.scanf() 함수 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)예시코드 :</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int x, y, z;</t>
-  </si>
-  <si>
-    <t>int* px, * py, * pz, * tmp;</t>
-  </si>
-  <si>
-    <t>px = &amp;x;</t>
-  </si>
-  <si>
-    <t>py = &amp;y;</t>
-  </si>
-  <si>
-    <t>pz = &amp;z;</t>
-  </si>
-  <si>
-    <t>scanf("%d", px); // scanf의 기능은 첫번째 매개변수의 형식대로 입력을 하면 두번째 매개변수의 주소공간에 입력한 값을 저장(px에 참조하고 있는 x에 저장)</t>
-  </si>
-  <si>
-    <t>scanf("%d", py);</t>
-  </si>
-  <si>
-    <t>scanf("%d", pz);</t>
-  </si>
-  <si>
-    <t>//printf("%d", *px);</t>
-  </si>
-  <si>
-    <t>/*tmp = py;</t>
-  </si>
-  <si>
-    <t>py = px;</t>
-  </si>
-  <si>
-    <t>px = tmp;</t>
-  </si>
-  <si>
-    <t>tmp = pz;</t>
-  </si>
-  <si>
-    <t>pz = px;</t>
-  </si>
-  <si>
-    <t>px = tmp;*/</t>
-  </si>
-  <si>
-    <t>tmp = py;</t>
-  </si>
-  <si>
-    <t>px = pz;</t>
-  </si>
-  <si>
-    <t>printf("%d %d %d", *px, *py, *pz);</t>
-  </si>
-  <si>
-    <t>(1)의미 : scanf의 기능은 첫번째 매개변수의 형식대로 입력을 하면 두번째 매개변수의 주소공간에 입력한 값을 저장(px가 참조하고 있는 x에 저장)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3460,7 +3394,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53EDAC2-69D8-41B7-8499-C3945599E82E}">
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3854,114 +3788,6 @@
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>414</v>
-      </c>
-      <c r="C98" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C99" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C101" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C102" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C103" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C105" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C106" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C107" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C108" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C110" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C111" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C112" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C113" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C114" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C115" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C117" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C118" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C119" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C122" t="s">
-        <v>432</v>
       </c>
     </row>
   </sheetData>
